--- a/risorse/Risorsa_16_Roadmap_24_Mesi.xlsx
+++ b/risorse/Risorsa_16_Roadmap_24_Mesi.xlsx
@@ -17,10 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="€ #,##0;-"/>
-  </numFmts>
-  <fonts count="6">
+  <numFmts count="0"/>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,34 +27,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <color rgb="001E3A5F"/>
+      <sz val="15"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="0000838F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
+      <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -65,21 +64,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000BCD4"/>
+        <fgColor rgb="001E3A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000A1F2E"/>
+        <fgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000838F"/>
+        <fgColor rgb="00F5A623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000A8E8"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -87,126 +91,34 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CFD8DC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CFD8DC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CFD8DC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CFD8DC"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CFD8DC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CFD8DC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CFD8DC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CFD8DC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CFD8DC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CFD8DC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CFD8DC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CFD8DC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C8E6C9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFF59D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFCDD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -571,31 +483,31 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AIOsha · Risorsa 16 — Roadmap AI 24 Mesi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>AI Osha — Risorsa 16 · Roadmap AI 24 Mesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pianificazione trimestrale con KPI</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+          <t>Pianificazione trimestrale con KPI. Il budget totale si calcola da solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Trimestre</t>
@@ -637,7 +549,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Q1 (mesi 1-3)</t>
@@ -653,9 +565,9 @@
           <t>Audit + 3 use case</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Diagnosi PMI, scelta tool, training base team, primi 3 prompt scaffold</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Diagnosi azienda, scelta tool, training base del team, primi 3 scaffold di prompt</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -663,7 +575,7 @@
           <t>Titolare</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="4" t="n">
         <v>500</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -671,53 +583,53 @@
           <t>100% team formato base; 3 use case attivi</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Da fare</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Q2 (mesi 4-6)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Calendario AI + newsletter</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>30gg calendario, 2 newsletter/mese, generazione visual con AI</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Marketing/Comunicazione</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
+          <t>Calendario 30 giorni, 2 newsletter/mese, generazione visual con AI</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Marketing / Comunicazione</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>800</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>+30% pubblicazioni; -50% tempo content</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>+30% pubblicazioni; -50% tempo contenuti</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Da fare</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Q3 (mesi 7-9)</t>
@@ -733,9 +645,9 @@
           <t>Preventivi e follow-up automatici</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Template offerta, sequenza follow-up, CRM minimo, recall dormienti</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Template offerta, sequenza follow-up, CRM minimo, recall clienti dormienti</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -743,7 +655,7 @@
           <t>Vendite</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="4" t="n">
         <v>600</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -751,26 +663,26 @@
           <t>Tempo preventivo -70%; +15% conversione</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Da fare</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Q4 (mesi 10-12)</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Customer care e admin</t>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Customer care e amministrazione</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -778,26 +690,26 @@
           <t>Triage mail AI, knowledge base interna, categorizzazione spese</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Admin/Customer care</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Amministrazione / Customer care</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>700</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Tempo risposta -60%; chiusura mese in 1 giorno</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Da fare</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Q5 (mesi 13-15)</t>
@@ -813,17 +725,17 @@
           <t>Primi 2 agenti AI</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Workflow lead-routing, agent estrai-dati fatture</t>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Workflow lead-routing, agente estrai-dati da fatture</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>IT/Operations</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
+          <t>IT / Operations</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>1500</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -831,53 +743,53 @@
           <t>2 agenti in produzione; ROI &gt; 3x</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Da fare</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Q6 (mesi 16-18)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Policy e ruoli</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Pubblicazione policy AI, formazione legal/compliance, audit semestrale</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+          <t>Pubblicazione policy AI, formazione compliance, audit semestrale</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Direzione</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>100% staff firma policy; 0 incidenti AI</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>100% staff firma la policy; 0 incidenti AI</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Da fare</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Q7 (mesi 19-21)</t>
@@ -893,9 +805,9 @@
           <t>Differenziazione di mercato</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Servizio AI-augmented per clienti, case study pubblici</t>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Servizio potenziato con AI per i clienti, case study pubblici</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -903,7 +815,7 @@
           <t>Direzione + Marketing</t>
         </is>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="4" t="n">
         <v>1200</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -911,47 +823,47 @@
           <t>1 servizio AI lanciato; +10% lead inbound</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Da fare</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Q8 (mesi 22-24)</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Scala</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Sistematizzazione e miglioramento continuo</t>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Sistematizzazione e miglioramento</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Review intero stack, retraining team, roadmap anno 3</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+          <t>Review dell'intero stack, retraining team, roadmap anno 3</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Tutto il team</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="5" t="n">
         <v>800</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Saturazione AI &gt; 60%; NPS interno &gt; 8</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Uso AI &gt; 60%; NPS interno &gt; 8</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Da fare</t>
         </is>
@@ -963,32 +875,12 @@
           <t>BUDGET TOTALE 24 MESI</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="10">
+      <c r="F13" s="7">
         <f>SUM(F5:F12)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="H5:H12">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"Completato"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"In corso"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
-      <formula>"Da fare"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1029,400 +921,228 @@
     <col width="4" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AIOsha · Gantt visivo 24 mesi</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>AI Osha — Gantt visivo 24 mesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cella colorata = trimestre attivo</t>
+          <t>Le celle colorate indicano il trimestre attivo per ogni tema.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Tema</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>M6</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>M7</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>M8</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>M12</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="9" t="inlineStr">
         <is>
           <t>M13</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t>M14</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="9" t="inlineStr">
         <is>
           <t>M15</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q4" s="9" t="inlineStr">
         <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R4" s="9" t="inlineStr">
         <is>
           <t>M17</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="9" t="inlineStr">
         <is>
           <t>M18</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T4" s="9" t="inlineStr">
         <is>
           <t>M19</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="U4" s="9" t="inlineStr">
         <is>
           <t>M20</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="V4" s="9" t="inlineStr">
         <is>
           <t>M21</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>M22</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="X4" s="9" t="inlineStr">
         <is>
           <t>M23</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="Y4" s="9" t="inlineStr">
         <is>
           <t>M24</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Fondamenta</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr"/>
-      <c r="C5" s="11" t="inlineStr"/>
-      <c r="D5" s="11" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr"/>
-      <c r="Y5" s="4" t="inlineStr"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="11" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr"/>
-      <c r="G6" s="11" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Vendite</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="11" t="inlineStr"/>
-      <c r="I7" s="11" t="inlineStr"/>
-      <c r="J7" s="11" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="11" t="inlineStr"/>
-      <c r="L8" s="11" t="inlineStr"/>
-      <c r="M8" s="11" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr"/>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Automazioni</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="11" t="inlineStr"/>
-      <c r="P9" s="11" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr"/>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="11" t="inlineStr"/>
-      <c r="R10" s="11" t="inlineStr"/>
-      <c r="S10" s="11" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="inlineStr"/>
+      <c r="Q10" s="10" t="n"/>
+      <c r="R10" s="10" t="n"/>
+      <c r="S10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Vantaggio competitivo</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
-      <c r="U11" s="11" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr"/>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="10" t="n"/>
+      <c r="V11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Scala</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="4" t="inlineStr"/>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr"/>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="11" t="inlineStr"/>
-      <c r="X12" s="11" t="inlineStr"/>
-      <c r="Y12" s="11" t="inlineStr"/>
+      <c r="W12" s="10" t="n"/>
+      <c r="X12" s="10" t="n"/>
+      <c r="Y12" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>